--- a/data/performance/daily/signal_list_2026-05-27.xlsx
+++ b/data/performance/daily/signal_list_2026-05-27.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 45.5%  (5W / 6L of 11 evaluated, 1 pending)</t>
+          <t>Win Rate: 36.4%  (4W / 7L of 11 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4420</v>
+        <v>4480</v>
       </c>
       <c r="D6" t="n">
         <v>4270</v>
@@ -585,10 +585,10 @@
         <v>4440</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.45</v>
+        <v>-0.89</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.39</v>
+        <v>-4.69</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D7" t="n">
         <v>156</v>
@@ -627,10 +627,10 @@
         <v>159</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.63</v>
+        <v>1.27</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.27</v>
+        <v>-0.64</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D9" t="n">
         <v>1135</v>
@@ -711,10 +711,10 @@
         <v>1145</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.09</v>
+        <v>5.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.18</v>
+        <v>4.13</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13525</v>
+        <v>15350</v>
       </c>
       <c r="D10" t="n">
         <v>13550</v>
@@ -753,14 +753,14 @@
         <v>14100</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.25</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-11.73</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D12" t="n">
         <v>250</v>
@@ -837,10 +837,10 @@
         <v>256</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.34</v>
+        <v>9.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.76</v>
+        <v>6.84</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D14" t="n">
         <v>422</v>
@@ -921,10 +921,10 @@
         <v>430</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.82</v>
+        <v>11.4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.76</v>
+        <v>9.33</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D15" t="n">
         <v>500</v>
@@ -963,10 +963,10 @@
         <v>515</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.91</v>
+        <v>-0.99</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 45.8%  (11W / 13L of 24 evaluated, 1 pending)</t>
+          <t>Win Rate: 37.5%  (9W / 15L of 24 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2890</v>
+        <v>2910</v>
       </c>
       <c r="D8" t="n">
         <v>2890</v>
@@ -1255,10 +1255,10 @@
         <v>2890</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4420</v>
+        <v>4480</v>
       </c>
       <c r="D9" t="n">
         <v>4270</v>
@@ -1297,10 +1297,10 @@
         <v>4440</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.45</v>
+        <v>-0.89</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.39</v>
+        <v>-4.69</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1485</v>
+        <v>1440</v>
       </c>
       <c r="D10" t="n">
         <v>1500</v>
@@ -1339,10 +1339,10 @@
         <v>1505</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.35</v>
+        <v>4.51</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.01</v>
+        <v>4.17</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D11" t="n">
         <v>1135</v>
@@ -1381,10 +1381,10 @@
         <v>1145</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.09</v>
+        <v>5.05</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.18</v>
+        <v>4.13</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1900</v>
+        <v>1895</v>
       </c>
       <c r="D12" t="n">
         <v>1825</v>
@@ -1423,10 +1423,10 @@
         <v>1920</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.95</v>
+        <v>-3.69</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D13" t="n">
         <v>298</v>
@@ -1465,10 +1465,10 @@
         <v>318</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.63</v>
+        <v>1.27</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.7</v>
+        <v>-5.1</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16700</v>
+        <v>16850</v>
       </c>
       <c r="D14" t="n">
         <v>16675</v>
@@ -1507,10 +1507,10 @@
         <v>16750</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.59</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.15</v>
+        <v>-1.04</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="D15" t="n">
         <v>600</v>
@@ -1549,10 +1549,10 @@
         <v>640</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.25</v>
+        <v>-7.69</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2900</v>
+        <v>3090</v>
       </c>
       <c r="D16" t="n">
         <v>3030</v>
@@ -1591,14 +1591,14 @@
         <v>3170</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9.31</v>
+        <v>2.59</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.94</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13525</v>
+        <v>15350</v>
       </c>
       <c r="D17" t="n">
         <v>13550</v>
@@ -1633,14 +1633,14 @@
         <v>14100</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.25</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-11.73</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="D19" t="n">
         <v>750</v>
@@ -1717,10 +1717,10 @@
         <v>750</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.74</v>
+        <v>4.17</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.74</v>
+        <v>4.17</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D22" t="n">
         <v>250</v>
@@ -1843,10 +1843,10 @@
         <v>256</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.34</v>
+        <v>9.4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>7.76</v>
+        <v>6.84</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D23" t="n">
         <v>126</v>
@@ -1885,10 +1885,10 @@
         <v>126</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.61</v>
+        <v>9.57</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.61</v>
+        <v>9.57</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D25" t="n">
         <v>422</v>
@@ -1969,10 +1969,10 @@
         <v>430</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.82</v>
+        <v>11.4</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8.76</v>
+        <v>9.33</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D26" t="n">
         <v>500</v>
@@ -2011,10 +2011,10 @@
         <v>515</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.91</v>
+        <v>-0.99</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D27" t="n">
         <v>138</v>
@@ -2053,10 +2053,10 @@
         <v>148</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.23</v>
+        <v>6.47</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.82</v>
+        <v>-0.72</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
